--- a/Cosas que llegan de mercado/2026/Periodo 1/Nota5 (1).xlsx
+++ b/Cosas que llegan de mercado/2026/Periodo 1/Nota5 (1).xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luis\Documents\Refaccionaria\Planned request\Mercado\26\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\GitHub\Motozom\Cosas que llegan de mercado\2026\Periodo 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B5A5FC6-8680-41B3-AED6-35CB3F94DE10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7650"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="5">
   <si>
     <t>Cantidad</t>
   </si>
@@ -37,11 +38,14 @@
   <si>
     <t>Total</t>
   </si>
+  <si>
+    <t>SI LLEGO COMPLETO</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -128,7 +132,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Imagen 1"/>
+        <xdr:cNvPr id="2" name="Imagen 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -166,7 +176,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Imagen 2"/>
+        <xdr:cNvPr id="3" name="Imagen 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -204,7 +220,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Imagen 3"/>
+        <xdr:cNvPr id="4" name="Imagen 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -242,7 +264,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Imagen 4"/>
+        <xdr:cNvPr id="5" name="Imagen 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -530,11 +558,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="K2:O362"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="11" max="13" width="11.42578125" style="2"/>
+    <col min="14" max="14" width="36.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="11:15" x14ac:dyDescent="0.25">
@@ -562,6 +591,9 @@
         <f>K3*L3</f>
         <v>438</v>
       </c>
+      <c r="N3" t="s">
+        <v>4</v>
+      </c>
       <c r="O3">
         <f>SUM(M3:M102)</f>
         <v>2673</v>
@@ -646,49 +678,49 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="11:14" x14ac:dyDescent="0.25">
       <c r="M17" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="11:14" x14ac:dyDescent="0.25">
       <c r="M18" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="11:14" x14ac:dyDescent="0.25">
       <c r="M19" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="11:14" x14ac:dyDescent="0.25">
       <c r="M20" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="11:14" x14ac:dyDescent="0.25">
       <c r="M21" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="11:14" x14ac:dyDescent="0.25">
       <c r="M22" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="11:14" x14ac:dyDescent="0.25">
       <c r="M23" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="11:14" x14ac:dyDescent="0.25">
       <c r="K24" s="2">
         <v>3</v>
       </c>
@@ -699,128 +731,131 @@
         <f t="shared" si="0"/>
         <v>558</v>
       </c>
-    </row>
-    <row r="25" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="N24" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="11:14" x14ac:dyDescent="0.25">
       <c r="M25" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="11:14" x14ac:dyDescent="0.25">
       <c r="M26" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="11:14" x14ac:dyDescent="0.25">
       <c r="M27" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="11:14" x14ac:dyDescent="0.25">
       <c r="M28" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="11:14" x14ac:dyDescent="0.25">
       <c r="M29" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="11:14" x14ac:dyDescent="0.25">
       <c r="M30" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="11:14" x14ac:dyDescent="0.25">
       <c r="M31" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="11:14" x14ac:dyDescent="0.25">
       <c r="M32" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="11:14" x14ac:dyDescent="0.25">
       <c r="M33" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="11:14" x14ac:dyDescent="0.25">
       <c r="M34" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="11:14" x14ac:dyDescent="0.25">
       <c r="M35" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="11:14" x14ac:dyDescent="0.25">
       <c r="M36" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="37" spans="11:14" x14ac:dyDescent="0.25">
       <c r="M37" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="11:14" x14ac:dyDescent="0.25">
       <c r="M38" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="39" spans="11:14" x14ac:dyDescent="0.25">
       <c r="M39" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="40" spans="11:14" x14ac:dyDescent="0.25">
       <c r="M40" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="41" spans="11:14" x14ac:dyDescent="0.25">
       <c r="M41" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="42" spans="11:14" x14ac:dyDescent="0.25">
       <c r="M42" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="11:14" x14ac:dyDescent="0.25">
       <c r="M43" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="44" spans="11:14" x14ac:dyDescent="0.25">
       <c r="M44" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="45" spans="11:14" x14ac:dyDescent="0.25">
       <c r="K45" s="2">
         <v>2</v>
       </c>
@@ -831,20 +866,23 @@
         <f t="shared" si="0"/>
         <v>972</v>
       </c>
-    </row>
-    <row r="46" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="N45" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="11:14" x14ac:dyDescent="0.25">
       <c r="M46" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="47" spans="11:14" x14ac:dyDescent="0.25">
       <c r="M47" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="48" spans="11:14" x14ac:dyDescent="0.25">
       <c r="M48" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -946,37 +984,37 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="65" spans="11:14" x14ac:dyDescent="0.25">
       <c r="M65" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="66" spans="11:14" x14ac:dyDescent="0.25">
       <c r="M66" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="67" spans="11:14" x14ac:dyDescent="0.25">
       <c r="M67" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="68" spans="11:14" x14ac:dyDescent="0.25">
       <c r="M68" s="2">
         <f t="shared" ref="M68:M131" si="1">K68*L68</f>
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="69" spans="11:14" x14ac:dyDescent="0.25">
       <c r="M69" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="70" spans="11:14" x14ac:dyDescent="0.25">
       <c r="K70" s="2">
         <v>3</v>
       </c>
@@ -987,62 +1025,65 @@
         <f t="shared" si="1"/>
         <v>705</v>
       </c>
-    </row>
-    <row r="71" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="N70" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" spans="11:14" x14ac:dyDescent="0.25">
       <c r="M71" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="72" spans="11:14" x14ac:dyDescent="0.25">
       <c r="M72" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="73" spans="11:14" x14ac:dyDescent="0.25">
       <c r="M73" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="74" spans="11:14" x14ac:dyDescent="0.25">
       <c r="M74" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="75" spans="11:14" x14ac:dyDescent="0.25">
       <c r="M75" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="76" spans="11:14" x14ac:dyDescent="0.25">
       <c r="M76" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="77" spans="11:14" x14ac:dyDescent="0.25">
       <c r="M77" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="78" spans="11:14" x14ac:dyDescent="0.25">
       <c r="M78" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="79" spans="11:14" x14ac:dyDescent="0.25">
       <c r="M79" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="11:13" x14ac:dyDescent="0.25">
+    <row r="80" spans="11:14" x14ac:dyDescent="0.25">
       <c r="M80" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
